--- a/toy_models/farm_toy_v4_optimizer.xlsx
+++ b/toy_models/farm_toy_v4_optimizer.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A139"/>
+  <dimension ref="A1:A165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -1292,137 +1292,295 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>WHAT v4 STILL DOES NOT CARRY</t>
+          <t>!! THE TWO BIGGEST THINGS v4 DOES NOT DO — and one of them dwarfs the rest</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Costs are seed/transplant per acre ONLY. No labour, water, fuel, packaging, storage or</t>
+          <t>Raised by the grower on first reading, and both were missing from this list. Measured before</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">    overhead. So the profit figure is far too high, deliberately — v5 adds the cash layer.</t>
+          <t>being written down.</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - No cash-flow constraint, so it can spend money it does not have.</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Shelf life is still a WARNING, not enforced.</t>
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>1. IT DOES NOT CHOOSE WHEN TO PLANT.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Three crops and five plantings, against seven and 220 on the real farm.</t>
+          <t xml:space="preserve">   The app's calendar generator offers 68 possible plantings for these three crops — one per</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   legal start week — and the real solver allocates acres across ALL of them, so choosing the</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>!! THE SCALE WARNING — it matters more here than anywhere</t>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   planting weeks is part of what it decides. v4 offers five, which I picked by hand.</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Small models are TIGHT, large ones LOOSE. An optimizer's answer is far more scale-sensitive</t>
-        </is>
-      </c>
+      <c r="A127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>than a calculator's: which constraints bind, and therefore which crop wins, can invert</t>
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Freeing that one restriction: profit $1,094,831 -&gt; $2,493,974. +128%.</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>entirely between 3 crops and 7. Do not read this plan as advice about your farm. Read it as</t>
-        </is>
-      </c>
+      <c r="A129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>a demonstration of what the machinery does.</t>
+          <t xml:space="preserve">   It plants 42 of the 68, staggered thinly across many start weeks — which is succession</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   planting, and the reason the practice exists. Spreading the harvest lets you serve a</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>HAS THIS SHEET BEEN CHECKED?</t>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   WEEKLY demand cap continuously instead of dumping one big harvest into a few weeks and</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Yes, and v4 adds a check the others could not have. Crop constants, planting dates and demand</t>
+          <t xml:space="preserve">   hitting the ceiling. My five-succession sheet cannot express that at all, so it understates</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>caps are read from the app. The formulas are calculated by an engine and compared cell by</t>
+          <t xml:space="preserve">   by more than every missing cost line combined.</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>cell against an independent model. Every input is perturbed to prove it propagates. No number</t>
-        </is>
-      </c>
+      <c r="A135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>is frozen. AND: the same LP is solved with scipy.milp, its answer written into the OFFERED</t>
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>2. IT HAS NO PLANT / DO-NOT-PLANT DECISION.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>cells, and the sheet's own PROFIT cell must reproduce the optimum exactly — which proves the</t>
+          <t xml:space="preserve">   The real model is a MILP: a binary y per succession, tied to x by C9 and C10, so a crop</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>spreadsheet and the solver are the same problem.</t>
+          <t xml:space="preserve">   that IS planted must meet its minimum acreage. v4 is a pure LP with no binaries, which</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   leaves it free to plant a third of an acre. Of the 42 plantings above, TEN are below the</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   app's own 2-acre minimum, totalling 12.7 acres of slivers the real model forbids.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>These two pull in OPPOSITE directions — the fixed calendar understates, the missing binaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>overstate — so neither number can be quoted on its own. Both land in v5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>WHAT v4 STILL DOES NOT CARRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Costs are seed/transplant per acre ONLY. No labour, water, fuel, packaging, storage or</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    overhead. So the profit figure is far too high, deliberately — v5 adds the cash layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - No cash-flow constraint, so it can spend money it does not have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Shelf life is still a WARNING, not enforced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Three crops and five plantings, against seven and 220 on the real farm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>!! THE SCALE WARNING — it matters more here than anywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Small models are TIGHT, large ones LOOSE. An optimizer's answer is far more scale-sensitive</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>than a calculator's: which constraints bind, and therefore which crop wins, can invert</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>entirely between 3 crops and 7. Do not read this plan as advice about your farm. Read it as</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>a demonstration of what the machinery does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>HAS THIS SHEET BEEN CHECKED?</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Yes, and v4 adds a check the others could not have. Crop constants, planting dates and demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>caps are read from the app. The formulas are calculated by an engine and compared cell by</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>cell against an independent model. Every input is perturbed to prove it propagates. No number</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>is frozen. AND: the same LP is solved with scipy.milp, its answer written into the OFFERED</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>cells, and the sheet's own PROFIT cell must reproduce the optimum exactly — which proves the</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>spreadsheet and the solver are the same problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t xml:space="preserve">     Run it yourself:   .venv/bin/python toy_models/verify_toy_v4.py</t>
         </is>
